--- a/ig/ch-elm/StructureDefinition-PublishDocumentReference.xlsx
+++ b/ig/ch-elm/StructureDefinition-PublishDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1419,7 +1419,7 @@
     <t>This list of codes represents the main clinical acts being documented.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActCode|2018-08-12</t>
   </si>
   <si>
     <t>Composition.event.code</t>

--- a/ig/ch-elm/StructureDefinition-PublishDocumentReference.xlsx
+++ b/ig/ch-elm/StructureDefinition-PublishDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1419,7 +1419,7 @@
     <t>This list of codes represents the main clinical acts being documented.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActCode|2018-08-12</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActCode|3.0.0</t>
   </si>
   <si>
     <t>Composition.event.code</t>

--- a/ig/ch-elm/StructureDefinition-PublishDocumentReference.xlsx
+++ b/ig/ch-elm/StructureDefinition-PublishDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-PublishDocumentReference.xlsx
+++ b/ig/ch-elm/StructureDefinition-PublishDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
